--- a/jogos_2026-07-07.xlsx
+++ b/jogos_2026-07-07.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -721,68 +721,68 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -880,68 +880,68 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>

--- a/jogos_2026-07-07.xlsx
+++ b/jogos_2026-07-07.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -721,68 +721,68 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -880,68 +880,68 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>

--- a/jogos_2026-07-07.xlsx
+++ b/jogos_2026-07-07.xlsx
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>

--- a/jogos_2026-07-07.xlsx
+++ b/jogos_2026-07-07.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -721,68 +721,68 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.53</v>
+        <v>2.12</v>
       </c>
       <c r="O2" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="P2" t="n">
-        <v>4.8</v>
+        <v>3.66</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -880,68 +880,68 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.12</v>
+        <v>1.53</v>
       </c>
       <c r="O3" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="P3" t="n">
-        <v>3.66</v>
+        <v>4.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>

--- a/jogos_2026-07-07.xlsx
+++ b/jogos_2026-07-07.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -721,68 +721,68 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.12</v>
+        <v>1.53</v>
       </c>
       <c r="O2" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="P2" t="n">
-        <v>3.66</v>
+        <v>4.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -880,68 +880,68 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.53</v>
+        <v>2.12</v>
       </c>
       <c r="O3" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="P3" t="n">
-        <v>4.8</v>
+        <v>3.66</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>

--- a/jogos_2026-07-07.xlsx
+++ b/jogos_2026-07-07.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU3"/>
+  <dimension ref="A1:AU4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -988,6 +988,165 @@
       </c>
       <c r="AU3" s="3" t="n">
         <v>46210.83333333334</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>SD Aucas</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Guayaquil City FC</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="O4" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="P4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" s="3" t="n">
+        <v>46210.875</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2026-07-07.xlsx
+++ b/jogos_2026-07-07.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -721,69 +721,69 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.53</v>
+        <v>2.12</v>
       </c>
       <c r="O2" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="P2" t="n">
-        <v>4.8</v>
+        <v>3.66</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.15</v>
+        <v>3.22</v>
       </c>
       <c r="R2" t="n">
-        <v>2.5</v>
+        <v>1.84</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2</v>
+        <v>1.52</v>
       </c>
       <c r="T2" t="n">
-        <v>3.88</v>
+        <v>2.33</v>
       </c>
       <c r="U2" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF2" t="n">
         <v>2</v>
       </c>
-      <c r="V2" t="n">
+      <c r="AG2" t="n">
         <v>1.71</v>
       </c>
-      <c r="W2" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>[]</t>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.15</v>
+        <v>1.55</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -880,68 +880,68 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.12</v>
+        <v>1.53</v>
       </c>
       <c r="O3" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="P3" t="n">
-        <v>3.66</v>
+        <v>4.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>

--- a/jogos_2026-07-07.xlsx
+++ b/jogos_2026-07-07.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -721,68 +721,68 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.12</v>
+        <v>1.53</v>
       </c>
       <c r="O2" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="P2" t="n">
-        <v>3.66</v>
+        <v>4.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.22</v>
+        <v>2.15</v>
       </c>
       <c r="R2" t="n">
-        <v>1.84</v>
+        <v>2.5</v>
       </c>
       <c r="S2" t="n">
-        <v>1.52</v>
+        <v>1.2</v>
       </c>
       <c r="T2" t="n">
-        <v>2.33</v>
+        <v>3.88</v>
       </c>
       <c r="U2" t="n">
-        <v>3.44</v>
+        <v>2</v>
       </c>
       <c r="V2" t="n">
-        <v>1.24</v>
+        <v>1.71</v>
       </c>
       <c r="W2" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="X2" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.44</v>
+        <v>1.12</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.65</v>
+        <v>6.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.43</v>
+        <v>1.35</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.75</v>
+        <v>2.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.16</v>
+        <v>1.8</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="AF2" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.71</v>
+        <v>2.7</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.55</v>
+        <v>2.15</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -880,69 +880,69 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.53</v>
+        <v>2.12</v>
       </c>
       <c r="O3" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="P3" t="n">
-        <v>4.8</v>
+        <v>3.66</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.15</v>
+        <v>3.22</v>
       </c>
       <c r="R3" t="n">
-        <v>2.5</v>
+        <v>1.84</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2</v>
+        <v>1.52</v>
       </c>
       <c r="T3" t="n">
-        <v>3.88</v>
+        <v>2.33</v>
       </c>
       <c r="U3" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF3" t="n">
         <v>2</v>
       </c>
-      <c r="V3" t="n">
+      <c r="AG3" t="n">
         <v>1.71</v>
       </c>
-      <c r="W3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>[]</t>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.15</v>
+        <v>1.55</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>

--- a/jogos_2026-07-07.xlsx
+++ b/jogos_2026-07-07.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -721,69 +721,69 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.53</v>
+        <v>2.12</v>
       </c>
       <c r="O2" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="P2" t="n">
-        <v>4.8</v>
+        <v>3.66</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.15</v>
+        <v>3.22</v>
       </c>
       <c r="R2" t="n">
-        <v>2.5</v>
+        <v>1.84</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2</v>
+        <v>1.52</v>
       </c>
       <c r="T2" t="n">
-        <v>3.88</v>
+        <v>2.33</v>
       </c>
       <c r="U2" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF2" t="n">
         <v>2</v>
       </c>
-      <c r="V2" t="n">
+      <c r="AG2" t="n">
         <v>1.71</v>
       </c>
-      <c r="W2" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>[]</t>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.15</v>
+        <v>1.55</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -880,68 +880,68 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.12</v>
+        <v>1.53</v>
       </c>
       <c r="O3" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="P3" t="n">
-        <v>3.66</v>
+        <v>4.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.22</v>
+        <v>2.15</v>
       </c>
       <c r="R3" t="n">
-        <v>1.84</v>
+        <v>2.5</v>
       </c>
       <c r="S3" t="n">
-        <v>1.52</v>
+        <v>1.2</v>
       </c>
       <c r="T3" t="n">
-        <v>2.33</v>
+        <v>3.88</v>
       </c>
       <c r="U3" t="n">
-        <v>3.44</v>
+        <v>2</v>
       </c>
       <c r="V3" t="n">
-        <v>1.24</v>
+        <v>1.71</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="X3" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.44</v>
+        <v>1.12</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.65</v>
+        <v>6.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.43</v>
+        <v>1.35</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.75</v>
+        <v>2.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.16</v>
+        <v>1.8</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.71</v>
+        <v>2.7</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.55</v>
+        <v>2.15</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>

--- a/jogos_2026-07-07.xlsx
+++ b/jogos_2026-07-07.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -721,68 +721,68 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.12</v>
+        <v>1.53</v>
       </c>
       <c r="O2" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="P2" t="n">
-        <v>3.66</v>
+        <v>4.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.22</v>
+        <v>2.15</v>
       </c>
       <c r="R2" t="n">
-        <v>1.84</v>
+        <v>2.5</v>
       </c>
       <c r="S2" t="n">
-        <v>1.52</v>
+        <v>1.2</v>
       </c>
       <c r="T2" t="n">
-        <v>2.33</v>
+        <v>3.88</v>
       </c>
       <c r="U2" t="n">
-        <v>3.44</v>
+        <v>2</v>
       </c>
       <c r="V2" t="n">
-        <v>1.24</v>
+        <v>1.71</v>
       </c>
       <c r="W2" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="X2" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.44</v>
+        <v>1.12</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.65</v>
+        <v>6.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.43</v>
+        <v>1.35</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.75</v>
+        <v>2.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.16</v>
+        <v>1.8</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="AF2" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.71</v>
+        <v>2.7</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.55</v>
+        <v>2.15</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -880,68 +880,68 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.53</v>
+        <v>2.3</v>
       </c>
       <c r="O3" t="n">
-        <v>4.2</v>
+        <v>2.94</v>
       </c>
       <c r="P3" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.15</v>
+        <v>3.22</v>
       </c>
       <c r="R3" t="n">
-        <v>2.5</v>
+        <v>1.84</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2</v>
+        <v>1.55</v>
       </c>
       <c r="T3" t="n">
-        <v>3.88</v>
+        <v>2.33</v>
       </c>
       <c r="U3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF3" t="n">
         <v>2</v>
       </c>
-      <c r="V3" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AG3" t="n">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.15</v>
+        <v>1.55</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>

--- a/jogos_2026-07-07.xlsx
+++ b/jogos_2026-07-07.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -721,68 +721,68 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.53</v>
+        <v>2.3</v>
       </c>
       <c r="O2" t="n">
-        <v>4.2</v>
+        <v>2.87</v>
       </c>
       <c r="P2" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.15</v>
+        <v>3.22</v>
       </c>
       <c r="R2" t="n">
-        <v>2.5</v>
+        <v>1.84</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2</v>
+        <v>1.55</v>
       </c>
       <c r="T2" t="n">
-        <v>3.88</v>
+        <v>2.33</v>
       </c>
       <c r="U2" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF2" t="n">
         <v>2</v>
       </c>
-      <c r="V2" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AG2" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.15</v>
+        <v>1.55</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -880,68 +880,68 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.3</v>
+        <v>1.49</v>
       </c>
       <c r="O3" t="n">
-        <v>2.94</v>
+        <v>4</v>
       </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.22</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.84</v>
+        <v>2.55</v>
       </c>
       <c r="S3" t="n">
-        <v>1.55</v>
+        <v>1.22</v>
       </c>
       <c r="T3" t="n">
-        <v>2.33</v>
+        <v>3.58</v>
       </c>
       <c r="U3" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="V3" t="n">
-        <v>1.24</v>
+        <v>1.7</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X3" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.48</v>
+        <v>1.12</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.65</v>
+        <v>4.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.43</v>
+        <v>1.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.5</v>
+        <v>2.71</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.65</v>
+        <v>2.08</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.12</v>
+        <v>1.73</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.03</v>
+        <v>1.29</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.55</v>
+        <v>2.45</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1052,55 +1052,55 @@
         <v>6.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="R4" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="S4" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T4" t="n">
-        <v>2.98</v>
+        <v>2.78</v>
       </c>
       <c r="U4" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="V4" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W4" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.27</v>
+        <v>3.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE4" t="n">
         <v>1.1</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>

--- a/jogos_2026-07-07.xlsx
+++ b/jogos_2026-07-07.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -721,68 +721,68 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.3</v>
+        <v>1.49</v>
       </c>
       <c r="O2" t="n">
-        <v>2.87</v>
+        <v>4</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.22</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.84</v>
+        <v>2.55</v>
       </c>
       <c r="S2" t="n">
-        <v>1.55</v>
+        <v>1.22</v>
       </c>
       <c r="T2" t="n">
-        <v>2.33</v>
+        <v>3.58</v>
       </c>
       <c r="U2" t="n">
-        <v>3.44</v>
+        <v>2.1</v>
       </c>
       <c r="V2" t="n">
-        <v>1.24</v>
+        <v>1.7</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="X2" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.48</v>
+        <v>1.12</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.65</v>
+        <v>4.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.43</v>
+        <v>1.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.5</v>
+        <v>2.71</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.65</v>
+        <v>2.08</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.12</v>
+        <v>1.73</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.05</v>
+        <v>1.29</v>
       </c>
       <c r="AF2" t="n">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.7</v>
+        <v>2.45</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.55</v>
+        <v>2.45</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -880,69 +880,69 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.49</v>
+        <v>2.3</v>
       </c>
       <c r="O3" t="n">
-        <v>4</v>
+        <v>2.87</v>
       </c>
       <c r="P3" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF3" t="n">
         <v>2</v>
       </c>
-      <c r="R3" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V3" t="n">
+      <c r="AG3" t="n">
         <v>1.7</v>
       </c>
-      <c r="W3" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>[]</t>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.45</v>
+        <v>1.55</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>

--- a/jogos_2026-07-07.xlsx
+++ b/jogos_2026-07-07.xlsx
@@ -728,7 +728,7 @@
         <v>1.49</v>
       </c>
       <c r="O2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P2" t="n">
         <v>4.8</v>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O3" t="n">
         <v>2.87</v>
       </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q3" t="n">
         <v>3.22</v>
@@ -899,28 +899,28 @@
         <v>1.84</v>
       </c>
       <c r="S3" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="T3" t="n">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="U3" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="V3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
         <v>1.11</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="AA3" t="n">
         <v>2.43</v>
@@ -929,19 +929,19 @@
         <v>1.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.65</v>
+        <v>4.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF3" t="n">
         <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>1.36</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>

--- a/jogos_2026-07-07.xlsx
+++ b/jogos_2026-07-07.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -721,68 +721,68 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.49</v>
+        <v>2.4</v>
       </c>
       <c r="O2" t="n">
-        <v>4.1</v>
+        <v>2.87</v>
       </c>
       <c r="P2" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="Q2" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF2" t="n">
         <v>2</v>
       </c>
-      <c r="R2" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AG2" t="n">
-        <v>2.45</v>
+        <v>1.75</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -880,68 +880,68 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.4</v>
+        <v>1.49</v>
       </c>
       <c r="O3" t="n">
-        <v>2.87</v>
+        <v>4.1</v>
       </c>
       <c r="P3" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.22</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.84</v>
+        <v>2.55</v>
       </c>
       <c r="S3" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="T3" t="n">
-        <v>2.55</v>
+        <v>3.58</v>
       </c>
       <c r="U3" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="V3" t="n">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X3" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.44</v>
+        <v>1.12</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.63</v>
+        <v>4.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.43</v>
+        <v>1.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.5</v>
+        <v>2.71</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.9</v>
+        <v>2.08</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.17</v>
+        <v>1.73</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.02</v>
+        <v>1.29</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -1052,10 +1052,10 @@
         <v>6.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="R4" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S4" t="n">
         <v>1.36</v>
@@ -1064,10 +1064,10 @@
         <v>2.78</v>
       </c>
       <c r="U4" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="V4" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W4" t="n">
         <v>1.07</v>
@@ -1076,22 +1076,22 @@
         <v>1.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z4" t="n">
         <v>3.35</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AC4" t="n">
         <v>3.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE4" t="n">
         <v>1.1</v>

--- a/jogos_2026-07-07.xlsx
+++ b/jogos_2026-07-07.xlsx
@@ -731,7 +731,7 @@
         <v>2.87</v>
       </c>
       <c r="P2" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
         <v>3.22</v>

--- a/jogos_2026-07-07.xlsx
+++ b/jogos_2026-07-07.xlsx
@@ -1052,10 +1052,10 @@
         <v>6.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="R4" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="S4" t="n">
         <v>1.36</v>
@@ -1064,19 +1064,19 @@
         <v>2.78</v>
       </c>
       <c r="U4" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="V4" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
         <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Z4" t="n">
         <v>3.35</v>
@@ -1085,16 +1085,16 @@
         <v>1.91</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF4" t="n">
         <v>1.95</v>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>

--- a/jogos_2026-07-07.xlsx
+++ b/jogos_2026-07-07.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -721,68 +721,68 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.4</v>
+        <v>1.49</v>
       </c>
       <c r="O2" t="n">
-        <v>2.87</v>
+        <v>4.1</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.22</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.84</v>
+        <v>2.55</v>
       </c>
       <c r="S2" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="T2" t="n">
-        <v>2.55</v>
+        <v>3.58</v>
       </c>
       <c r="U2" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="V2" t="n">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="W2" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X2" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.44</v>
+        <v>1.12</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.63</v>
+        <v>4.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.43</v>
+        <v>1.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.5</v>
+        <v>2.71</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.9</v>
+        <v>2.08</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.17</v>
+        <v>1.73</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.02</v>
+        <v>1.29</v>
       </c>
       <c r="AF2" t="n">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -880,68 +880,68 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.49</v>
+        <v>2.4</v>
       </c>
       <c r="O3" t="n">
-        <v>4.1</v>
+        <v>2.87</v>
       </c>
       <c r="P3" t="n">
-        <v>4.8</v>
+        <v>2.97</v>
       </c>
       <c r="Q3" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF3" t="n">
         <v>2</v>
       </c>
-      <c r="R3" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AG3" t="n">
-        <v>2.45</v>
+        <v>1.75</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,34 +1043,34 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="O4" t="n">
-        <v>4.09</v>
+        <v>4.44</v>
       </c>
       <c r="P4" t="n">
-        <v>6.8</v>
+        <v>6.95</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="R4" t="n">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="S4" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T4" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V4" t="n">
         <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X4" t="n">
         <v>1</v>
@@ -1082,7 +1082,7 @@
         <v>3.35</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="AB4" t="n">
         <v>1.8</v>
@@ -1091,16 +1091,16 @@
         <v>3.25</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>

--- a/jogos_2026-07-07.xlsx
+++ b/jogos_2026-07-07.xlsx
@@ -728,7 +728,7 @@
         <v>1.49</v>
       </c>
       <c r="O2" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="P2" t="n">
         <v>4.8</v>
@@ -884,16 +884,16 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O3" t="n">
         <v>2.87</v>
       </c>
       <c r="P3" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="R3" t="n">
         <v>1.84</v>
@@ -905,22 +905,22 @@
         <v>2.33</v>
       </c>
       <c r="U3" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="V3" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AA3" t="n">
         <v>2.43</v>
@@ -929,13 +929,13 @@
         <v>1.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.9</v>
+        <v>4.91</v>
       </c>
       <c r="AD3" t="n">
         <v>1.17</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF3" t="n">
         <v>2</v>
@@ -1043,46 +1043,46 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="O4" t="n">
-        <v>4.44</v>
+        <v>4.09</v>
       </c>
       <c r="P4" t="n">
-        <v>6.95</v>
+        <v>6.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="R4" t="n">
-        <v>2.29</v>
+        <v>2.17</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T4" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="U4" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
         <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.72</v>
+        <v>1.93</v>
       </c>
       <c r="AB4" t="n">
         <v>1.8</v>
@@ -1091,16 +1091,16 @@
         <v>3.25</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>

--- a/jogos_2026-07-07.xlsx
+++ b/jogos_2026-07-07.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -721,68 +721,68 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.49</v>
+        <v>2.45</v>
       </c>
       <c r="O2" t="n">
-        <v>3.85</v>
+        <v>2.87</v>
       </c>
       <c r="P2" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF2" t="n">
         <v>2</v>
       </c>
-      <c r="R2" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AG2" t="n">
-        <v>2.45</v>
+        <v>1.75</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -880,69 +880,69 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AG3" t="n">
         <v>2.45</v>
       </c>
-      <c r="O3" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="P3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>[]</t>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1061,7 +1061,7 @@
         <v>1.37</v>
       </c>
       <c r="T4" t="n">
-        <v>2.96</v>
+        <v>2.77</v>
       </c>
       <c r="U4" t="n">
         <v>2.74</v>
@@ -1070,10 +1070,10 @@
         <v>1.39</v>
       </c>
       <c r="W4" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
         <v>1.3</v>
@@ -1082,16 +1082,16 @@
         <v>3.34</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AB4" t="n">
         <v>1.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.25</v>
+        <v>3.59</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE4" t="n">
         <v>1.1</v>

--- a/jogos_2026-07-07.xlsx
+++ b/jogos_2026-07-07.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -721,69 +721,69 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AG2" t="n">
         <v>2.45</v>
       </c>
-      <c r="O2" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="P2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>[]</t>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -880,68 +880,68 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.49</v>
+        <v>2.45</v>
       </c>
       <c r="O3" t="n">
-        <v>3.85</v>
+        <v>2.87</v>
       </c>
       <c r="P3" t="n">
-        <v>4.8</v>
+        <v>2.78</v>
       </c>
       <c r="Q3" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF3" t="n">
         <v>2</v>
       </c>
-      <c r="R3" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AG3" t="n">
-        <v>2.45</v>
+        <v>1.75</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1055,7 +1055,7 @@
         <v>1.99</v>
       </c>
       <c r="R4" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="S4" t="n">
         <v>1.37</v>
@@ -1067,7 +1067,7 @@
         <v>2.74</v>
       </c>
       <c r="V4" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="W4" t="n">
         <v>1.07</v>

--- a/jogos_2026-07-07.xlsx
+++ b/jogos_2026-07-07.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -721,68 +721,68 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.49</v>
+        <v>2.45</v>
       </c>
       <c r="O2" t="n">
-        <v>3.85</v>
+        <v>2.87</v>
       </c>
       <c r="P2" t="n">
-        <v>4.8</v>
+        <v>2.78</v>
       </c>
       <c r="Q2" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF2" t="n">
         <v>2</v>
       </c>
-      <c r="R2" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AG2" t="n">
-        <v>2.45</v>
+        <v>1.75</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -880,69 +880,69 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AG3" t="n">
         <v>2.45</v>
       </c>
-      <c r="O3" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U3" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>[]</t>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>

--- a/jogos_2026-07-07.xlsx
+++ b/jogos_2026-07-07.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -721,69 +721,69 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AG2" t="n">
         <v>2.45</v>
       </c>
-      <c r="O2" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U2" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>[]</t>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -880,68 +880,68 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.49</v>
+        <v>2.45</v>
       </c>
       <c r="O3" t="n">
-        <v>3.85</v>
+        <v>2.87</v>
       </c>
       <c r="P3" t="n">
-        <v>4.8</v>
+        <v>2.78</v>
       </c>
       <c r="Q3" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF3" t="n">
         <v>2</v>
       </c>
-      <c r="R3" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AG3" t="n">
-        <v>2.45</v>
+        <v>1.75</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="O4" t="n">
         <v>4.09</v>
@@ -1058,28 +1058,28 @@
         <v>2.25</v>
       </c>
       <c r="S4" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T4" t="n">
         <v>2.77</v>
       </c>
       <c r="U4" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="V4" t="n">
         <v>1.37</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.34</v>
+        <v>3.86</v>
       </c>
       <c r="AA4" t="n">
         <v>1.88</v>
@@ -1091,7 +1091,7 @@
         <v>3.59</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AE4" t="n">
         <v>1.1</v>

--- a/jogos_2026-07-07.xlsx
+++ b/jogos_2026-07-07.xlsx
@@ -905,22 +905,22 @@
         <v>2.33</v>
       </c>
       <c r="U3" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="V3" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="W3" t="n">
         <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AA3" t="n">
         <v>2.38</v>
@@ -1052,7 +1052,7 @@
         <v>6.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="R4" t="n">
         <v>2.25</v>
@@ -1070,7 +1070,7 @@
         <v>1.37</v>
       </c>
       <c r="W4" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
@@ -1082,10 +1082,10 @@
         <v>3.86</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC4" t="n">
         <v>3.59</v>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>

--- a/jogos_2026-07-07.xlsx
+++ b/jogos_2026-07-07.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -721,68 +721,68 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.49</v>
+        <v>2.45</v>
       </c>
       <c r="O2" t="n">
-        <v>3.85</v>
+        <v>2.87</v>
       </c>
       <c r="P2" t="n">
-        <v>4.8</v>
+        <v>2.78</v>
       </c>
       <c r="Q2" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF2" t="n">
         <v>2</v>
       </c>
-      <c r="R2" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AG2" t="n">
-        <v>2.45</v>
+        <v>1.75</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -880,69 +880,69 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="O3" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="P3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AG3" t="n">
         <v>2.45</v>
       </c>
-      <c r="O3" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>[]</t>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>

--- a/jogos_2026-07-07.xlsx
+++ b/jogos_2026-07-07.xlsx
@@ -746,16 +746,16 @@
         <v>2.33</v>
       </c>
       <c r="U2" t="n">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="V2" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="W2" t="n">
         <v>1.04</v>
       </c>
       <c r="X2" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Y2" t="n">
         <v>1.44</v>
@@ -776,7 +776,7 @@
         <v>1.17</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF2" t="n">
         <v>2</v>
@@ -1052,10 +1052,10 @@
         <v>6.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="R4" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S4" t="n">
         <v>1.36</v>
@@ -1070,7 +1070,7 @@
         <v>1.37</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
@@ -1091,7 +1091,7 @@
         <v>3.59</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AE4" t="n">
         <v>1.1</v>

--- a/jogos_2026-07-07.xlsx
+++ b/jogos_2026-07-07.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -721,69 +721,69 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="O2" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="P2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AG2" t="n">
         <v>2.45</v>
       </c>
-      <c r="O2" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U2" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>[]</t>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -880,68 +880,68 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.49</v>
+        <v>2.45</v>
       </c>
       <c r="O3" t="n">
-        <v>4.25</v>
+        <v>2.87</v>
       </c>
       <c r="P3" t="n">
-        <v>4.8</v>
+        <v>2.78</v>
       </c>
       <c r="Q3" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF3" t="n">
         <v>2</v>
       </c>
-      <c r="R3" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AG3" t="n">
-        <v>2.45</v>
+        <v>1.75</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>

--- a/jogos_2026-07-07.xlsx
+++ b/jogos_2026-07-07.xlsx
@@ -728,7 +728,7 @@
         <v>1.49</v>
       </c>
       <c r="O2" t="n">
-        <v>4.25</v>
+        <v>3.85</v>
       </c>
       <c r="P2" t="n">
         <v>4.8</v>
@@ -884,31 +884,31 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O3" t="n">
         <v>2.87</v>
       </c>
       <c r="P3" t="n">
-        <v>2.78</v>
+        <v>3.08</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.23</v>
+        <v>3.18</v>
       </c>
       <c r="R3" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="S3" t="n">
         <v>1.5</v>
       </c>
       <c r="T3" t="n">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="U3" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="V3" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="W3" t="n">
         <v>1.04</v>
@@ -929,13 +929,13 @@
         <v>1.53</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.91</v>
+        <v>4.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF3" t="n">
         <v>2</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="O4" t="n">
-        <v>4.09</v>
+        <v>4.05</v>
       </c>
       <c r="P4" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="S4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T4" t="n">
-        <v>2.77</v>
+        <v>2.98</v>
       </c>
       <c r="U4" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="V4" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W4" t="n">
         <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.86</v>
+        <v>3.45</v>
       </c>
       <c r="AA4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB4" t="n">
         <v>1.85</v>
       </c>
-      <c r="AB4" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AC4" t="n">
-        <v>3.59</v>
+        <v>3.62</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AE4" t="n">
         <v>1.1</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>

--- a/jogos_2026-07-07.xlsx
+++ b/jogos_2026-07-07.xlsx
@@ -902,19 +902,19 @@
         <v>1.5</v>
       </c>
       <c r="T3" t="n">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="U3" t="n">
         <v>3.6</v>
       </c>
       <c r="V3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W3" t="n">
         <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Y3" t="n">
         <v>1.44</v>
@@ -923,10 +923,10 @@
         <v>2.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AC3" t="n">
         <v>4.9</v>
@@ -1046,10 +1046,10 @@
         <v>1.35</v>
       </c>
       <c r="O4" t="n">
-        <v>4.05</v>
+        <v>4.01</v>
       </c>
       <c r="P4" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="Q4" t="n">
         <v>2</v>
@@ -1058,16 +1058,16 @@
         <v>2.13</v>
       </c>
       <c r="S4" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T4" t="n">
-        <v>2.98</v>
+        <v>2.7</v>
       </c>
       <c r="U4" t="n">
         <v>2.78</v>
       </c>
       <c r="V4" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
         <v>1.08</v>
@@ -1076,10 +1076,10 @@
         <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="AA4" t="n">
         <v>1.9</v>
@@ -1097,7 +1097,7 @@
         <v>1.1</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AG4" t="n">
         <v>1.67</v>
@@ -1116,7 +1116,7 @@
         <v>1.22</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.52</v>
+        <v>2.39</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>

--- a/jogos_2026-07-07.xlsx
+++ b/jogos_2026-07-07.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -721,68 +721,68 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.49</v>
+        <v>2.18</v>
       </c>
       <c r="O2" t="n">
-        <v>3.85</v>
+        <v>2.87</v>
       </c>
       <c r="P2" t="n">
-        <v>4.8</v>
+        <v>3.08</v>
       </c>
       <c r="Q2" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF2" t="n">
         <v>2</v>
       </c>
-      <c r="R2" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AG2" t="n">
-        <v>2.45</v>
+        <v>1.75</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.45</v>
+        <v>1.5</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -880,68 +880,68 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.4</v>
+        <v>1.49</v>
       </c>
       <c r="O3" t="n">
-        <v>2.87</v>
+        <v>3.85</v>
       </c>
       <c r="P3" t="n">
-        <v>3.08</v>
+        <v>4.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.18</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="T3" t="n">
-        <v>2.32</v>
+        <v>3.58</v>
       </c>
       <c r="U3" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="V3" t="n">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="W3" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="X3" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.44</v>
+        <v>1.12</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.5</v>
+        <v>4.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.5</v>
+        <v>2.71</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.9</v>
+        <v>2.08</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.18</v>
+        <v>1.73</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.05</v>
+        <v>1.29</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.5</v>
+        <v>2.45</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>

--- a/jogos_2026-07-07.xlsx
+++ b/jogos_2026-07-07.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -721,68 +721,68 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.18</v>
+        <v>1.49</v>
       </c>
       <c r="O2" t="n">
-        <v>2.87</v>
+        <v>3.85</v>
       </c>
       <c r="P2" t="n">
-        <v>3.08</v>
+        <v>4.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.18</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="S2" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="T2" t="n">
-        <v>2.32</v>
+        <v>3.58</v>
       </c>
       <c r="U2" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="V2" t="n">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="W2" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="X2" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.44</v>
+        <v>1.12</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.5</v>
+        <v>4.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.5</v>
+        <v>2.71</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.9</v>
+        <v>2.08</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.17</v>
+        <v>1.73</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.05</v>
+        <v>1.29</v>
       </c>
       <c r="AF2" t="n">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.5</v>
+        <v>2.45</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -880,68 +880,68 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.49</v>
+        <v>2.18</v>
       </c>
       <c r="O3" t="n">
-        <v>3.85</v>
+        <v>2.87</v>
       </c>
       <c r="P3" t="n">
-        <v>4.8</v>
+        <v>3.08</v>
       </c>
       <c r="Q3" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF3" t="n">
         <v>2</v>
       </c>
-      <c r="R3" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AG3" t="n">
-        <v>2.45</v>
+        <v>1.75</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.45</v>
+        <v>1.5</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="O4" t="n">
-        <v>4.01</v>
+        <v>3.9</v>
       </c>
       <c r="P4" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="Q4" t="n">
         <v>2</v>
@@ -1064,22 +1064,22 @@
         <v>2.7</v>
       </c>
       <c r="U4" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W4" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AA4" t="n">
         <v>1.9</v>
@@ -1088,19 +1088,19 @@
         <v>1.85</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.62</v>
+        <v>3.25</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE4" t="n">
         <v>1.1</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>

--- a/jogos_2026-07-07.xlsx
+++ b/jogos_2026-07-07.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -721,68 +721,68 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.49</v>
+        <v>2.18</v>
       </c>
       <c r="O2" t="n">
-        <v>3.85</v>
+        <v>2.78</v>
       </c>
       <c r="P2" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC2" t="n">
         <v>4.8</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="AD2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF2" t="n">
         <v>2</v>
       </c>
-      <c r="R2" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AG2" t="n">
-        <v>2.45</v>
+        <v>1.75</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.45</v>
+        <v>1.52</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -880,68 +880,68 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.18</v>
+        <v>1.62</v>
       </c>
       <c r="O3" t="n">
-        <v>2.87</v>
+        <v>4.15</v>
       </c>
       <c r="P3" t="n">
-        <v>3.08</v>
+        <v>4.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.18</v>
+        <v>2.15</v>
       </c>
       <c r="R3" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="S3" t="n">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="T3" t="n">
-        <v>2.32</v>
+        <v>4.2</v>
       </c>
       <c r="U3" t="n">
-        <v>3.6</v>
+        <v>1.99</v>
       </c>
       <c r="V3" t="n">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="W3" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="X3" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.44</v>
+        <v>1.12</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.5</v>
+        <v>1.36</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.9</v>
+        <v>2.08</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.17</v>
+        <v>1.8</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.05</v>
+        <v>1.29</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>1.41</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.75</v>
+        <v>2.66</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1052,55 +1052,55 @@
         <v>6.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="R4" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="S4" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T4" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="U4" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="V4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W4" t="n">
         <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.5</v>
+        <v>3.86</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AB4" t="n">
         <v>1.85</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.25</v>
+        <v>3.59</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>1.22</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.39</v>
+        <v>2.52</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>

--- a/jogos_2026-07-07.xlsx
+++ b/jogos_2026-07-07.xlsx
@@ -725,25 +725,25 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="O2" t="n">
-        <v>2.78</v>
+        <v>2.95</v>
       </c>
       <c r="P2" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.22</v>
+        <v>3.44</v>
       </c>
       <c r="R2" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="S2" t="n">
         <v>1.53</v>
       </c>
       <c r="T2" t="n">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="U2" t="n">
         <v>3.6</v>
@@ -752,37 +752,37 @@
         <v>1.25</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AD2" t="n">
         <v>1.11</v>
       </c>
-      <c r="Y2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AE2" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF2" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>1.33</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -880,38 +880,38 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="O3" t="n">
-        <v>4.15</v>
+        <v>3.85</v>
       </c>
       <c r="P3" t="n">
-        <v>4.8</v>
+        <v>5.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="R3" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T3" t="n">
-        <v>4.2</v>
+        <v>3.58</v>
       </c>
       <c r="U3" t="n">
-        <v>1.99</v>
+        <v>2.11</v>
       </c>
       <c r="V3" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="X3" t="n">
         <v>1.01</v>
@@ -920,28 +920,28 @@
         <v>1.12</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.5</v>
+        <v>4.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AE3" t="n">
         <v>1.29</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.66</v>
+        <v>2.25</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>

--- a/jogos_2026-07-07.xlsx
+++ b/jogos_2026-07-07.xlsx
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="O4" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="P4" t="n">
-        <v>6.9</v>
+        <v>8.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="R4" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="S4" t="n">
         <v>1.38</v>
       </c>
       <c r="T4" t="n">
-        <v>2.74</v>
+        <v>3.02</v>
       </c>
       <c r="U4" t="n">
-        <v>2.74</v>
+        <v>2.89</v>
       </c>
       <c r="V4" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="W4" t="n">
         <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.86</v>
+        <v>3.65</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.59</v>
+        <v>3.25</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE4" t="n">
         <v>1.09</v>
       </c>
       <c r="AF4" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.52</v>
+        <v>2.77</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>

--- a/jogos_2026-07-07.xlsx
+++ b/jogos_2026-07-07.xlsx
@@ -734,7 +734,7 @@
         <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.44</v>
+        <v>3.48</v>
       </c>
       <c r="R2" t="n">
         <v>1.79</v>
@@ -758,19 +758,19 @@
         <v>1.08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="Z2" t="n">
         <v>2.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AB2" t="n">
         <v>1.41</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="AD2" t="n">
         <v>1.11</v>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AK2" t="n">
         <v>1.53</v>

--- a/jogos_2026-07-07.xlsx
+++ b/jogos_2026-07-07.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.3</v>
+        <v>1.38</v>
       </c>
       <c r="O2" t="n">
-        <v>2.95</v>
+        <v>3.85</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>5.75</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.48</v>
+        <v>1.9</v>
       </c>
       <c r="R2" t="n">
-        <v>1.79</v>
+        <v>2.55</v>
       </c>
       <c r="S2" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="T2" t="n">
-        <v>2.23</v>
+        <v>3.58</v>
       </c>
       <c r="U2" t="n">
-        <v>3.6</v>
+        <v>2.11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.25</v>
+        <v>1.66</v>
       </c>
       <c r="W2" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="X2" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.5</v>
+        <v>1.12</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.6</v>
+        <v>4.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.63</v>
+        <v>1.41</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.41</v>
+        <v>2.56</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.75</v>
+        <v>2.09</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.11</v>
+        <v>1.67</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.03</v>
+        <v>1.29</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.11</v>
+        <v>1.57</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.53</v>
+        <v>2.7</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,19 +852,19 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -876,115 +876,115 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.38</v>
+        <v>2.3</v>
       </c>
       <c r="O3" t="n">
-        <v>3.85</v>
+        <v>2.95</v>
       </c>
       <c r="P3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC3" t="n">
         <v>5.75</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U3" t="n">
+      <c r="AD3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF3" t="n">
         <v>2.11</v>
       </c>
-      <c r="V3" t="n">
+      <c r="AG3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>['54']</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>1.66</v>
       </c>
-      <c r="W3" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46210.83333333334</v>
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="O4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="P4" t="n">
         <v>8.25</v>
@@ -1055,52 +1055,52 @@
         <v>1.85</v>
       </c>
       <c r="R4" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="S4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="V4" t="n">
         <v>1.38</v>
       </c>
-      <c r="T4" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.41</v>
-      </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="AC4" t="n">
         <v>3.25</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
